--- a/sheets/대금율보/검수/꽃타령.xlsx
+++ b/sheets/대금율보/검수/꽃타령.xlsx
@@ -6638,8 +6638,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -6649,8 +6648,7 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -6660,8 +6658,7 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-‹</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="G6" s="24"/>
@@ -6669,8 +6666,7 @@
       <c r="I6" s="24"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K6" s="24" t="inlineStr">
@@ -6692,8 +6688,7 @@
       </c>
       <c r="N6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O6" s="24" t="inlineStr">
@@ -7027,8 +7022,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋ʒ
-‹</t>
+          <t xml:space="preserve">淋ʒ</t>
         </is>
       </c>
       <c r="G10" s="24" t="inlineStr">
@@ -7038,8 +7032,7 @@
       </c>
       <c r="H10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I10" s="24" t="inlineStr">
@@ -7069,8 +7062,7 @@
       <c r="O10" s="24"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="Q10" s="24" t="inlineStr">
@@ -7468,8 +7460,7 @@
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -7479,8 +7470,7 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G14" s="24" t="inlineStr">
@@ -7523,8 +7513,7 @@
       </c>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="O14" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/꽃타령.xlsx
+++ b/sheets/대금율보/검수/꽃타령.xlsx
@@ -6265,32 +6265,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="10.71" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6317,7 +6317,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
       <c r="T5" s="21"/>
       <c r="U5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
       <c r="T6" s="21"/>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
       <c r="T7" s="21"/>
       <c r="U7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
       <c r="T8" s="21"/>
       <c r="U8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
       <c r="T9" s="21"/>
       <c r="U9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="U10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -7663,7 +7663,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -7985,6 +7985,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>